--- a/output/gpu_prices_2026-08-01.xlsx
+++ b/output/gpu_prices_2026-08-01.xlsx
@@ -434,15 +434,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,25 +462,70 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>DigitalOcean</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Hot Aisle</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Hyperstack</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Lambda Labs</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>LeaderGPU</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Massed Compute</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Ori</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Paperspace</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>QuantaCloud</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Scaleway</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ThunderCompute</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>VERDA</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Vast.ai</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Vultr</t>
         </is>
@@ -480,230 +534,1174 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA A16</t>
+          <t>AMD Instinct MI300X</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="n">
+        <v>2.99</v>
+      </c>
       <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="n">
-        <v>0.47</v>
-      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA A30</t>
+          <t>Intel Gaudi 2</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.35</v>
-      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="n">
+        <v>0.9114625</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce GTX 1080</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>0.3</v>
-      </c>
+          <t>NVIDIA A10</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 2080 Ti</t>
+          <t>NVIDIA A100 PCIe 40GB</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="n">
-        <v>0.12</v>
-      </c>
+      <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 3060</t>
+          <t>NVIDIA A100 PCIe 80GB</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr"/>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="n">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 3090</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0.29</v>
-      </c>
+          <t>NVIDIA A100 SXM4 40GB</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="n">
-        <v>0.25</v>
+        <v>1.99</v>
       </c>
       <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 4060 Ti</t>
+          <t>NVIDIA A100 SXM4 80GB</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr"/>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="n">
-        <v>0.15</v>
+        <v>2.79</v>
       </c>
       <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="O8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 4090</t>
+          <t>NVIDIA A16</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr"/>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="n">
+        <v>0.471</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 5060 Ti</t>
+          <t>NVIDIA A30</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr"/>
       <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="n">
-        <v>0.18</v>
-      </c>
+      <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 5070</t>
+          <t>NVIDIA A40</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr"/>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="n">
+        <v>0.515625</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="n">
+        <v>0.075</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 5070 Ti</t>
+          <t>NVIDIA B200 SXM</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr"/>
       <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="E12" s="3" t="inlineStr"/>
       <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce RTX 5090</t>
+          <t>NVIDIA B300 SXM6</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr"/>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="n">
-        <v>0.45</v>
-      </c>
+      <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA L4</t>
+          <t>NVIDIA GH200 Grace Hopper</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr"/>
       <c r="C14" s="3" t="inlineStr"/>
       <c r="D14" s="3" t="inlineStr"/>
       <c r="E14" s="3" t="n">
-        <v>0.33</v>
+        <v>2.29</v>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 4000 Ada Generation</t>
+          <t>NVIDIA GeForce GTX 1080</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr"/>
       <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA RTX A4000</t>
+          <t>NVIDIA GeForce GTX 1080 Ti</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr"/>
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA RTX A5000</t>
+          <t>NVIDIA GeForce RTX 2080 Ti</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr"/>
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="n">
-        <v>0.23</v>
-      </c>
+      <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA GeForce RTX 3060</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="O18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA GeForce RTX 3090</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="n">
+        <v>0.2859375</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA GeForce RTX 4060 Ti</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="n">
+        <v>0.14665</v>
+      </c>
+      <c r="O20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA GeForce RTX 4090</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA GeForce RTX 5060 Ti</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="O22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA GeForce RTX 5070</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA GeForce RTX 5070 Ti</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA GeForce RTX 5090</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="n">
+        <v>0.4533</v>
+      </c>
+      <c r="O25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA H100 NVL</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="n">
+        <v>2.1813</v>
+      </c>
+      <c r="O26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA H100 PCIe</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>3.2922</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA H100 SXM5</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>3.392857142857143</v>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="n">
+        <v>3.8014</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>4.6667</v>
+      </c>
+      <c r="O28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA H200 NVL</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="n">
+        <v>4.68665</v>
+      </c>
+      <c r="O29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA H200 SXM</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA L4</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>0.9044</v>
+      </c>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA L40</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="K32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA L40S</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>1.6882</v>
+      </c>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA Quadro P4000</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr"/>
+      <c r="K34" s="3" t="inlineStr"/>
+      <c r="L34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA Quadro P5000</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA Quadro P6000</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr"/>
+      <c r="M36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr"/>
+      <c r="O36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA Quadro RTX 4000</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="inlineStr"/>
+      <c r="L37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA Quadro RTX 5000</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr"/>
+      <c r="C38" s="3" t="inlineStr"/>
+      <c r="D38" s="3" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr"/>
+      <c r="I38" s="3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
+      <c r="M38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr"/>
+      <c r="O38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA RTX 4000 Ada Generation</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="O39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA RTX 6000 Ada Generation</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr"/>
+      <c r="D40" s="3" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="3" t="n">
+        <v>1.1197875</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr"/>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>1.32535</v>
+      </c>
+      <c r="O40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA RTX A4000</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr"/>
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA RTX A5000</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr"/>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="n">
+        <v>0.2306714285714285</v>
+      </c>
+      <c r="O42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA RTX A6000</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA RTX PRO 6000 Blackwell</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="n">
+        <v>2.3825</v>
+      </c>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA Tesla P100</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
+      <c r="O45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA Tesla V100 16GB</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr"/>
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA Tesla V100 32GB</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr"/>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
